--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487419_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487419_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8292</v>
+        <v>3.9399</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9139</v>
+        <v>2.4256</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9153</v>
+        <v>1.5143</v>
       </c>
       <c r="G2" t="n">
         <v>3.9681</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1389</v>
+        <v>-1.0282</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7227</v>
+        <v>-1.211</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5837</v>
+        <v>0.1828</v>
       </c>
       <c r="V2" t="n">
         <v>0.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9256</v>
+        <v>2.8989</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5385</v>
+        <v>0.264</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3871</v>
+        <v>2.6349</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5515</v>
+        <v>0.3006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2416</v>
+        <v>1.2453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7931</v>
+        <v>-0.9447</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9183</v>
+        <v>2.0484</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9394</v>
+        <v>2.6046</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0211</v>
+        <v>-0.5562</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4698</v>
+        <v>-1.7479</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6978</v>
+        <v>-1.3593</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.772</v>
+        <v>-0.3886</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3294</v>
+        <v>1.7626</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>4.3087</v>
+        <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1476</v>
+        <v>-0.4961</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3241</v>
+        <v>-0.8052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1764</v>
+        <v>0.3091</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3318</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2754</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6436</v>
+        <v>2.4435</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0555</v>
+        <v>1.7485</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5881</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>2.1463</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0475</v>
+        <v>-0.2476</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2664</v>
+        <v>-0.0406</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3139</v>
+        <v>-0.207</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8260999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4269</v>
+        <v>2.2092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0593</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3676</v>
+        <v>1.3871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3006</v>
+        <v>-0.5515</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2453</v>
+        <v>0.2416</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9447</v>
+        <v>-0.7931</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0484</v>
+        <v>1.9183</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6046</v>
+        <v>1.9394</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5562</v>
+        <v>-0.0211</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7479</v>
+        <v>-2.4698</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3593</v>
+        <v>-1.6978</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3886</v>
+        <v>-0.772</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7626</v>
+        <v>3.3294</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>4.3087</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9681</v>
+        <v>-0.5687</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0098</v>
+        <v>-0.3923</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0418</v>
+        <v>-0.1764</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3318</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3318</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.954</v>
+        <v>1.5981</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9533</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0007</v>
+        <v>1.0542</v>
       </c>
       <c r="G6" t="n">
         <v>-0.501</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0645</v>
+        <v>-0.2914</v>
       </c>
       <c r="T6" t="n">
-        <v>0.117</v>
+        <v>-0.2923</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0526</v>
+        <v>0.0009</v>
       </c>
       <c r="V6" t="n">
         <v>1.6071</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4305</v>
+        <v>-0.4038</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7806</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3501</v>
+        <v>0.3768</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3889</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2374</v>
+        <v>-0.2107</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7544</v>
+        <v>-0.6273</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6554</v>
+        <v>1.0338</v>
       </c>
       <c r="F8" t="n">
-        <v>0.901</v>
+        <v>-1.6611</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-2.1507</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3525</v>
+        <v>1.8363</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4142</v>
+        <v>-3.987</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4385</v>
+        <v>0.0576</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1225</v>
+        <v>3.5351</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-3.4776</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3281</v>
+        <v>-2.2083</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.475</v>
+        <v>-1.6988</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1468</v>
+        <v>-0.5095</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>3.7211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0122</v>
+        <v>-1.3983</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>-0.6575</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2498</v>
+        <v>-0.7408</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.5922</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2062</v>
+        <v>-0.8613</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8290999999999999</v>
+        <v>-1.6554</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0353</v>
+        <v>0.794</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1507</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8363</v>
+        <v>-0.3525</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.987</v>
+        <v>-0.4142</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0576</v>
+        <v>-0.4385</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5351</v>
+        <v>0.1225</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.4776</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2083</v>
+        <v>-0.3281</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6988</v>
+        <v>-0.475</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5095</v>
+        <v>0.1468</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7211</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9772</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8622</v>
+        <v>-0.2376</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.115</v>
+        <v>0.1429</v>
       </c>
       <c r="V9" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5922</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4111</v>
+        <v>-2.2111</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3401</v>
+        <v>-3.0331</v>
       </c>
       <c r="F10" t="n">
-        <v>0.929</v>
+        <v>0.822</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4618</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.166</v>
+        <v>0.0341</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>0.1882</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0472</v>
+        <v>-0.1541</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.35</v>
+        <v>-3.3592</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4051</v>
+        <v>-4.2004</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0551</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6049</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.706</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.387</v>
+        <v>-0.1823</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.319</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9977</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.627100000000002</v>
+        <v>5.626899999999999</v>
       </c>
       <c r="E12" t="n">
         <v>-2.8316</v>
       </c>
       <c r="F12" t="n">
-        <v>8.4587</v>
+        <v>8.458500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0104</v>
@@ -1390,13 +1390,13 @@
         <v>22.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0168</v>
+        <v>-5.016800000000001</v>
       </c>
       <c r="T12" t="n">
         <v>-3.7494</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2674</v>
+        <v>-1.2673</v>
       </c>
       <c r="V12" t="n">
         <v>1.8824</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.907400000000001</v>
+        <v>8.073700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9003</v>
+        <v>5.4676</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0071</v>
+        <v>2.6061</v>
       </c>
       <c r="G13" t="n">
         <v>7.4066</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8551</v>
+        <v>1.0214</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8379</v>
+        <v>0.4052</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0172</v>
+        <v>0.6162</v>
       </c>
       <c r="V13" t="n">
         <v>0.4291</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.623</v>
+        <v>0.3392</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1356</v>
+        <v>-1.099</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7586</v>
+        <v>1.4382</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3219</v>
+        <v>-3.1789</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0419</v>
+        <v>-0.4804</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3637</v>
+        <v>-2.6985</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.601</v>
+        <v>-1.581</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0408</v>
+        <v>1.0122</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6418</v>
+        <v>-2.5932</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2791</v>
+        <v>-1.5979</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001</v>
+        <v>-1.4926</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2781</v>
+        <v>-0.1053</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8666</v>
+        <v>0.4439</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4446</v>
+        <v>-0.1482</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4219</v>
+        <v>0.5921</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6659</v>
+        <v>1.7032</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6659</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. DIAZ VALIN</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.545</v>
+        <v>0.2626</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3813</v>
+        <v>-1.4426</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8364</v>
+        <v>1.7052</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5585</v>
+        <v>-0.3219</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1439</v>
+        <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4145</v>
+        <v>-0.3637</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7554</v>
+        <v>-0.601</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7554</v>
+        <v>0.0408</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6418</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1969</v>
+        <v>0.2791</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4145</v>
+        <v>0.2781</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1751</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0716</v>
+        <v>0.5061</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1782</v>
+        <v>0.1376</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2498</v>
+        <v>0.3685</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>P. DIAZ VALIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7155</v>
+        <v>-0.4472</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.02</v>
+        <v>-1.1767</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3045</v>
+        <v>0.7294</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1789</v>
+        <v>0.5585</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4804</v>
+        <v>0.1439</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6985</v>
+        <v>0.4145</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.581</v>
+        <v>0.7554</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0122</v>
+        <v>0.7554</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.5932</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5979</v>
+        <v>-0.1969</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4926</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1053</v>
+        <v>0.4145</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6108</v>
+        <v>0.1694</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0692</v>
+        <v>0.0265</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4585</v>
+        <v>0.1429</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.8772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8436</v>
+        <v>-0.8657</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9096</v>
+        <v>-2.0119</v>
       </c>
       <c r="F17" t="n">
-        <v>1.066</v>
+        <v>1.1462</v>
       </c>
       <c r="G17" t="n">
         <v>0.184</v>
@@ -1780,13 +1780,13 @@
         <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8786</v>
+        <v>0.8565</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2952</v>
+        <v>0.1929</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5834</v>
+        <v>0.6636</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3394</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3949</v>
+        <v>-0.9275</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1498</v>
+        <v>2.4568</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5447</v>
+        <v>-3.3843</v>
       </c>
       <c r="G18" t="n">
         <v>0.3085</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0536</v>
+        <v>0.4138</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0882</v>
+        <v>0.3952</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1419</v>
+        <v>0.0185</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4332</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>É. PINA HURTADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9682</v>
+        <v>-2.4957</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6033</v>
+        <v>-1.1486</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3648</v>
+        <v>-1.3472</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8779</v>
+        <v>1.0187</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0596</v>
+        <v>-0.0977</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8183</v>
+        <v>1.1164</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9864000000000001</v>
+        <v>2.4177</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1076</v>
+        <v>1.1908</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1212</v>
+        <v>1.2269</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8916</v>
+        <v>-1.3989</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.952</v>
+        <v>-1.2884</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9396</v>
+        <v>-0.1105</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1751</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1751</v>
+        <v>-4.1128</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7508</v>
+        <v>0.6233</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9487</v>
+        <v>-0.0041</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8021</v>
+        <v>0.6274</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6659</v>
+        <v>-1.3958</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3905</v>
+        <v>0.5507</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-1.9466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>É. PINA HURTADO</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0479</v>
+        <v>-3.8541</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3532</v>
+        <v>-2.115</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6947</v>
+        <v>-1.7391</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0187</v>
+        <v>-2.8779</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0977</v>
+        <v>-2.0596</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1164</v>
+        <v>-0.8183</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4177</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1908</v>
+        <v>-1.1076</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2269</v>
+        <v>0.1212</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3989</v>
+        <v>-1.8916</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2884</v>
+        <v>-0.952</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1105</v>
+        <v>-0.9396</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7419</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1128</v>
+        <v>-1.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0711</v>
+        <v>0.8649</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2088</v>
+        <v>0.437</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2799</v>
+        <v>0.4279</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3958</v>
+        <v>-0.6659</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5507</v>
+        <v>-0.3905</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9466</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6424</v>
+        <v>-5.7122</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.105499999999999</v>
+        <v>-7.3892</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4632</v>
+        <v>1.677</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0873</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8126</v>
+        <v>0.1176</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.891</v>
+        <v>-0.1747</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0785</v>
+        <v>0.2923</v>
       </c>
       <c r="V21" t="n">
         <v>0.1537</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6271</v>
+        <v>-5.6269</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.458400000000001</v>
+        <v>-8.458600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8316</v>
+        <v>2.831499999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0103</v>
+        <v>2.010300000000001</v>
       </c>
       <c r="H22" t="n">
         <v>-2.7133</v>
@@ -2170,13 +2170,13 @@
         <v>11.7509</v>
       </c>
       <c r="S22" t="n">
-        <v>5.0168</v>
+        <v>5.016900000000001</v>
       </c>
       <c r="T22" t="n">
         <v>1.2674</v>
       </c>
       <c r="U22" t="n">
-        <v>3.749400000000001</v>
+        <v>3.7494</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8824</v>
